--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE220F5F-DE05-43FB-AD09-5B11EBE729C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FB676E-300C-4E84-9413-96951C4BBBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8415" yWindow="-17610" windowWidth="23010" windowHeight="16845" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="1868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="1869">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -54919,17 +54919,84 @@
       <t xml:space="preserve"> Удалит все записи из child таблицы, которые идут с зависимым полем parent таблицы</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Правило!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Обязательно в SELECT должно быть поле, по которому происходит группировка. Если в выражении SELECT производится выборка по одному или нескольким столбцам и</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> также используются агрегатные функции</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, то необходимо использовать выражение GROUP BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="97" x14ac:knownFonts="1">
+  <fonts count="98" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -56012,9 +56079,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="200">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -56025,42 +56092,48 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -56068,57 +56141,60 @@
     <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="46" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="35" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="36" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="58" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="59" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="37" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="38" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -56126,22 +56202,13 @@
     <xf numFmtId="49" fontId="33" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="32" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="59" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="58" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -56156,49 +56223,52 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="59" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="59" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="62" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="58" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="58" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="47" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -56207,25 +56277,22 @@
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -56234,61 +56301,61 @@
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="53" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="46" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="46" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -56300,7 +56367,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -56318,59 +56385,65 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="40" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="69" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="59" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="59" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="86" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="87" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="58" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="58" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="85" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="86" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -56379,49 +56452,43 @@
     <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -56436,10 +56503,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="92" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="93" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -56448,90 +56518,90 @@
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="56" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="56" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="55" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="55" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="47" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="53" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -56549,52 +56619,52 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="50" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="97" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="70" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="97" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="47" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="96" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="69" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="96" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="51" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -58392,15 +58462,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>91440</xdr:colOff>
+      <xdr:colOff>95250</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:rowOff>53341</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1959676</xdr:colOff>
+      <xdr:colOff>1963486</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>973455</xdr:rowOff>
+      <xdr:rowOff>969645</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -58423,7 +58493,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11475720" y="3897631"/>
+          <a:off x="11477625" y="3872866"/>
           <a:ext cx="1868236" cy="916304"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -65410,8 +65480,8 @@
     </row>
     <row r="11" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="66"/>
-      <c r="B11" s="83" t="s">
-        <v>767</v>
+      <c r="B11" s="199" t="s">
+        <v>1868</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>679</v>
@@ -71937,7 +72007,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="39" type="noConversion"/>
+  <phoneticPr fontId="40" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -72089,7 +72159,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="108" t="s">
         <v>1253</v>
@@ -77958,7 +78028,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="39" type="noConversion"/>
+  <phoneticPr fontId="40" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D40" r:id="rId1" location=":~:text=%D0%94%D0%BB%D1%8F%20%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D1%86%D0%B8%D0%B8%20%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82%D0%B0%20UNIQUEIDENTIFIER" xr:uid="{8276130C-D262-49CA-89B1-D60C8C3E4E63}"/>
   </hyperlinks>

--- a/4 четверть_MSSQL.xlsx
+++ b/4 четверть_MSSQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FB676E-300C-4E84-9413-96951C4BBBED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DC770B-79EE-40C5-A08E-E4B4DFCF17FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13875" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Изучить" sheetId="21" r:id="rId1"/>
@@ -21,38 +21,39 @@
     <sheet name="TABLE rm, mv" sheetId="26" r:id="rId6"/>
     <sheet name="CREATE" sheetId="27" r:id="rId7"/>
     <sheet name="ALTER" sheetId="28" r:id="rId8"/>
-    <sheet name="INSERT" sheetId="30" r:id="rId9"/>
-    <sheet name="UPDATE" sheetId="33" r:id="rId10"/>
-    <sheet name="DELETE" sheetId="34" r:id="rId11"/>
-    <sheet name="SELECT" sheetId="15" r:id="rId12"/>
-    <sheet name="CURSOR" sheetId="54" r:id="rId13"/>
-    <sheet name="WHERE" sheetId="19" r:id="rId14"/>
-    <sheet name="ORDER BY -&gt;" sheetId="31" r:id="rId15"/>
-    <sheet name="TOP, OFFSET" sheetId="32" r:id="rId16"/>
-    <sheet name="SUM...-&gt;" sheetId="35" r:id="rId17"/>
-    <sheet name="OVER" sheetId="51" r:id="rId18"/>
-    <sheet name="GROUP HAVING" sheetId="36" r:id="rId19"/>
-    <sheet name="JOIN" sheetId="37" r:id="rId20"/>
-    <sheet name="UNIVERSEs" sheetId="38" r:id="rId21"/>
-    <sheet name="NAVCH" sheetId="39" r:id="rId22"/>
-    <sheet name="INT" sheetId="40" r:id="rId23"/>
-    <sheet name="DATE" sheetId="41" r:id="rId24"/>
-    <sheet name="JSON&gt;TAB&gt;SQL" sheetId="52" r:id="rId25"/>
-    <sheet name="TAB&gt;JSON&gt;APP" sheetId="53" r:id="rId26"/>
-    <sheet name="DECLARE" sheetId="43" r:id="rId27"/>
-    <sheet name="IF" sheetId="23" r:id="rId28"/>
-    <sheet name="WHILE" sheetId="44" r:id="rId29"/>
-    <sheet name="TRY" sheetId="45" r:id="rId30"/>
-    <sheet name="VIEW" sheetId="46" r:id="rId31"/>
-    <sheet name="TABLE vars, CTE" sheetId="47" r:id="rId32"/>
-    <sheet name="Trigger" sheetId="49" r:id="rId33"/>
-    <sheet name="Procedures" sheetId="48" r:id="rId34"/>
-    <sheet name="Transaction" sheetId="50" r:id="rId35"/>
-    <sheet name="template" sheetId="14" r:id="rId36"/>
-    <sheet name="Каскадное удаление" sheetId="16" r:id="rId37"/>
-    <sheet name="Транзакции" sheetId="17" r:id="rId38"/>
-    <sheet name="bc Массивы" sheetId="18" r:id="rId39"/>
-    <sheet name="bc JSON" sheetId="22" r:id="rId40"/>
+    <sheet name="&gt;MERGE&lt; дописать" sheetId="55" r:id="rId9"/>
+    <sheet name="INSERT" sheetId="30" r:id="rId10"/>
+    <sheet name="UPDATE" sheetId="33" r:id="rId11"/>
+    <sheet name="DELETE" sheetId="34" r:id="rId12"/>
+    <sheet name="SELECT" sheetId="15" r:id="rId13"/>
+    <sheet name="CURSOR" sheetId="54" r:id="rId14"/>
+    <sheet name="WHERE" sheetId="19" r:id="rId15"/>
+    <sheet name="ORDER BY -&gt;" sheetId="31" r:id="rId16"/>
+    <sheet name="TOP, OFFSET" sheetId="32" r:id="rId17"/>
+    <sheet name="SUM...-&gt;" sheetId="35" r:id="rId18"/>
+    <sheet name="OVER" sheetId="51" r:id="rId19"/>
+    <sheet name="GROUP HAVING" sheetId="36" r:id="rId20"/>
+    <sheet name="JOIN" sheetId="37" r:id="rId21"/>
+    <sheet name="UNIVERSEs" sheetId="38" r:id="rId22"/>
+    <sheet name="NAVCH" sheetId="39" r:id="rId23"/>
+    <sheet name="INT" sheetId="40" r:id="rId24"/>
+    <sheet name="DATE" sheetId="41" r:id="rId25"/>
+    <sheet name="JSON&gt;TAB&gt;SQL" sheetId="52" r:id="rId26"/>
+    <sheet name="TAB&gt;JSON&gt;APP" sheetId="53" r:id="rId27"/>
+    <sheet name="DECLARE" sheetId="43" r:id="rId28"/>
+    <sheet name="IF" sheetId="23" r:id="rId29"/>
+    <sheet name="WHILE" sheetId="44" r:id="rId30"/>
+    <sheet name="TRY" sheetId="45" r:id="rId31"/>
+    <sheet name="VIEW" sheetId="46" r:id="rId32"/>
+    <sheet name="TABLE vars, CTE" sheetId="47" r:id="rId33"/>
+    <sheet name="Trigger" sheetId="49" r:id="rId34"/>
+    <sheet name="Procedures" sheetId="48" r:id="rId35"/>
+    <sheet name="Transaction" sheetId="50" r:id="rId36"/>
+    <sheet name="template" sheetId="14" r:id="rId37"/>
+    <sheet name="Каскадное удаление" sheetId="16" r:id="rId38"/>
+    <sheet name="Транзакции" sheetId="17" r:id="rId39"/>
+    <sheet name="bc Массивы" sheetId="18" r:id="rId40"/>
+    <sheet name="bc JSON" sheetId="22" r:id="rId41"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="1869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2257" uniqueCount="1871">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -54978,17 +54979,191 @@
 </t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Важно!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Параметр </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>обязателен</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> при вызове
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CREATE PROCEDURE [dbo].[API_Roszdravnadzor]
+    @UserID uniqueidentifier,   -- без = NULL
+    @Entity varchar(50)         -- без = NULL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Параметр </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не обязателен</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> при вызове
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CREATE PROCEDURE [dbo].[API_Roszdravnadzor]
+    @UserID uniqueidentifier </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,   -- с = NULL
+    @Entity varchar(50) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= NULL</t>
+    </r>
+  </si>
+  <si>
+    <t>MERGE &lt;target_table&gt; AS T
+USING &lt;source_table_or_query&gt; AS S
+   ON &lt;условие сопоставления T и S&gt;
+WHEN MATCHED [AND &lt;доп. условие&gt;] THEN
+    UPDATE SET ...
+WHEN NOT MATCHED [BY TARGET] THEN
+    INSERT (...) VALUES (...)
+WHEN NOT MATCHED BY SOURCE THEN
+    DELETE;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="98" x14ac:knownFonts="1">
+  <fonts count="100" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -56079,9 +56254,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -56092,47 +56267,99 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="39" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="41" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="40" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="39" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="38" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="38" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="49" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="48" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="38" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="49" fontId="38" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="40" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -56141,74 +56368,22 @@
     <xf numFmtId="49" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="36" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="36" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="38" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="61" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -56223,37 +56398,49 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="33" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="30" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="66" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="64" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="49" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -56262,37 +56449,25 @@
     <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -56301,61 +56476,61 @@
     <xf numFmtId="49" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="25" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="27" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="55" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="26" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="48" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -56367,7 +56542,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -56385,110 +56560,110 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="17" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="70" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="61" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="61" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="88" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="89" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="59" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="59" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="86" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="87" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="43" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="41" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -56503,102 +56678,108 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="93" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="95" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="17" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="58" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="56" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="56" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="48" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="50" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="17" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="52" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="53" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="55" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -56613,62 +56794,62 @@
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="52" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="99" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="72" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="99" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="49" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="50" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="54" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="43" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="97" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="70" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="97" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="52" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -59839,6 +60020,159 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EA6674-336F-4905-8CC7-BE3D2DB29BA7}">
+  <sheetPr>
+    <tabColor theme="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E13"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="46" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="46"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="47" t="s">
+        <v>488</v>
+      </c>
+      <c r="D3" s="69" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C4" s="66" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46" t="s">
+        <v>490</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>493</v>
+      </c>
+      <c r="D5" s="46"/>
+    </row>
+    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B6" s="66" t="s">
+        <v>499</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B7" s="66" t="s">
+        <v>498</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D8" s="66" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C9" s="146" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C10" s="79" t="s">
+        <v>719</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B11" s="66" t="s">
+        <v>505</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C13" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{71703303-5B70-4508-9FB9-E0DF58B4FD29}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E11B2404-3BCE-4C18-8606-2DD385DF9F42}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -59995,7 +60329,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604A5B54-859D-4372-BCC7-7C5355B11405}">
   <sheetPr>
     <tabColor rgb="FFC00000"/>
@@ -60123,7 +60457,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1F646E2-B598-4143-89B5-75F807CE8970}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -61110,7 +61444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF63D703-6A75-4591-BE87-D5A0AC53BC53}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -61254,7 +61588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87C455FF-42A2-4363-8055-67FDFE85198A}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -63031,7 +63365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11FE68FF-B5B6-418F-87F3-26D52CCBDCD1}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -63918,7 +64252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6700157-0300-47A5-B44F-29D9810FA897}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -64796,7 +65130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5BD91E9-1EBE-4787-BA8F-72F81F37997A}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -65210,7 +65544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA4FF46A-E1B1-4DC0-89B6-77CE4454821D}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -65389,281 +65723,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15477BA0-499D-45E0-87E5-D7C7CA4BA6B4}">
-  <sheetPr>
-    <tabColor theme="8"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E34"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="2" customWidth="1"/>
-    <col min="2" max="2" width="58.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="46" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="47" t="s">
-        <v>678</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
-        <v>735</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
-        <v>694</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1759</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="47" t="s">
-        <v>711</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1756</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E8" s="46"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
-        <v>678</v>
-      </c>
-      <c r="D9" s="69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C10" s="166" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="66"/>
-      <c r="B11" s="199" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="66"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="2" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="66"/>
-      <c r="B13" s="83" t="s">
-        <v>785</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="77" t="s">
-        <v>683</v>
-      </c>
-      <c r="D14" s="69"/>
-    </row>
-    <row r="15" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="66"/>
-      <c r="B15" s="83" t="s">
-        <v>682</v>
-      </c>
-      <c r="C15" s="66" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="47" t="s">
-        <v>735</v>
-      </c>
-      <c r="D16" s="69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C17" s="166" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C18" s="66" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="C19" s="2" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="77" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="C22" s="2" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="47" t="s">
-        <v>694</v>
-      </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C24" s="166" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="C25" s="79" t="s">
-        <v>707</v>
-      </c>
-      <c r="D25" s="79" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B26" s="32"/>
-      <c r="C26" s="2" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="66" t="s">
-        <v>703</v>
-      </c>
-      <c r="B27" s="66" t="s">
-        <v>701</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="66" t="s">
-        <v>702</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="47" t="s">
-        <v>705</v>
-      </c>
-      <c r="D29" s="69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="B30" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C30" s="79" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="47" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="C32" s="79" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="47" t="s">
-        <v>711</v>
-      </c>
-      <c r="B33" s="72" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="144" x14ac:dyDescent="0.3">
-      <c r="B34" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="C34" s="166" t="s">
-        <v>713</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" xr:uid="{77CDA991-63F1-40E4-A41F-F96B264AF4B3}"/>
-    <hyperlink ref="D16" r:id="rId2" location=":~:text=%D0%A4%D0%B8%D0%BB%D1%8C%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%20%D0%B3%D1%80%D1%83%D0%BF%D0%BF.%20HAVING" xr:uid="{7964F6FF-2EAF-4BD3-82D2-37627A9ACFD4}"/>
-    <hyperlink ref="D23" r:id="rId3" xr:uid="{B3944A25-C0A8-4BEB-926A-B7D97A16EF2A}"/>
-    <hyperlink ref="D29" r:id="rId4" location=":~:text=CUBE%20%D0%BF%D0%BE%D1%85%D0%BE%D0%B6%20%D0%BD%D0%B0%20ROLLUP" xr:uid="{9459E309-91A9-438D-BEC6-62FD725247A9}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId5"/>
-  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -65873,6 +65932,281 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15477BA0-499D-45E0-87E5-D7C7CA4BA6B4}">
+  <sheetPr>
+    <tabColor theme="8"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E34"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="58.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="46" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="47" t="s">
+        <v>735</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1758</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="47" t="s">
+        <v>694</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="47" t="s">
+        <v>711</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1756</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E8" s="46"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="47" t="s">
+        <v>678</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C10" s="166" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="66"/>
+      <c r="B11" s="199" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="66"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="66"/>
+      <c r="B13" s="83" t="s">
+        <v>785</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="77" t="s">
+        <v>683</v>
+      </c>
+      <c r="D14" s="69"/>
+    </row>
+    <row r="15" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="66"/>
+      <c r="B15" s="83" t="s">
+        <v>682</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="47" t="s">
+        <v>735</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C17" s="166" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C18" s="66" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="C19" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="77" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="C22" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="47" t="s">
+        <v>694</v>
+      </c>
+      <c r="C23" s="32"/>
+      <c r="D23" s="69" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C24" s="166" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="C25" s="79" t="s">
+        <v>707</v>
+      </c>
+      <c r="D25" s="79" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="B26" s="32"/>
+      <c r="C26" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="66" t="s">
+        <v>703</v>
+      </c>
+      <c r="B27" s="66" t="s">
+        <v>701</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="66" t="s">
+        <v>702</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="47" t="s">
+        <v>705</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="B30" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C30" s="79" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="47" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="C32" s="79" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="47" t="s">
+        <v>711</v>
+      </c>
+      <c r="B33" s="72" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="144" x14ac:dyDescent="0.3">
+      <c r="B34" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C34" s="166" t="s">
+        <v>713</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{77CDA991-63F1-40E4-A41F-F96B264AF4B3}"/>
+    <hyperlink ref="D16" r:id="rId2" location=":~:text=%D0%A4%D0%B8%D0%BB%D1%8C%D1%82%D1%80%D0%B0%D1%86%D0%B8%D1%8F%20%D0%B3%D1%80%D1%83%D0%BF%D0%BF.%20HAVING" xr:uid="{7964F6FF-2EAF-4BD3-82D2-37627A9ACFD4}"/>
+    <hyperlink ref="D23" r:id="rId3" xr:uid="{B3944A25-C0A8-4BEB-926A-B7D97A16EF2A}"/>
+    <hyperlink ref="D29" r:id="rId4" location=":~:text=CUBE%20%D0%BF%D0%BE%D1%85%D0%BE%D0%B6%20%D0%BD%D0%B0%20ROLLUP" xr:uid="{9459E309-91A9-438D-BEC6-62FD725247A9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId5"/>
+  <drawing r:id="rId6"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD905863-01CE-479F-877D-B25CFB17F8C9}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -66188,7 +66522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E627795B-0F65-49D8-8875-E3878397B251}">
   <sheetPr>
     <tabColor theme="8"/>
@@ -66398,7 +66732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA2B658-8DD3-4355-BA32-205FF02DBD74}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -66818,7 +67152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07071483-68B8-4A83-8459-BC9077F7B963}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -67240,7 +67574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F45C4F92-001F-4E91-8F03-EB46A8027543}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -67734,7 +68068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC1F7D4E-E918-443B-B8C8-416DF0748EEB}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -69017,7 +69351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A06BB25D-2DF2-411F-9C84-639C5F568AAC}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -69489,7 +69823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B618FF8A-AEBE-4109-8CD3-90151CF88DFD}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -69772,7 +70106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4794FD93-B283-45AF-BCD9-82490C321ADD}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -70652,876 +70986,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39B1FF9-091B-40BE-9FD0-8662822E487B}">
-  <sheetPr>
-    <tabColor rgb="FF7030A0"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:V52"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="8"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="U2" s="5"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" s="70" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="69" t="s">
-        <v>106</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="2"/>
-    </row>
-    <row r="4" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="108" t="s">
-        <v>1234</v>
-      </c>
-      <c r="P4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="2"/>
-    </row>
-    <row r="5" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="108" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C5" s="108" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" spans="1:22" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="108" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C6" s="108" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" s="107" t="s">
-        <v>1237</v>
-      </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="108" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="1"/>
-    </row>
-    <row r="22" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="1"/>
-    </row>
-    <row r="23" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="1"/>
-    </row>
-    <row r="24" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="1"/>
-    </row>
-    <row r="25" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="1"/>
-    </row>
-    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="1"/>
-    </row>
-    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="1"/>
-    </row>
-    <row r="28" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="2"/>
-      <c r="V28" s="1"/>
-    </row>
-    <row r="29" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="1"/>
-    </row>
-    <row r="30" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="P30" s="2"/>
-      <c r="Q30" s="2"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="2"/>
-      <c r="V30" s="1"/>
-    </row>
-    <row r="31" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="P31" s="2"/>
-      <c r="Q31" s="2"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="2"/>
-      <c r="V31" s="1"/>
-    </row>
-    <row r="32" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="1"/>
-    </row>
-    <row r="33" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="P33" s="2"/>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="1"/>
-    </row>
-    <row r="34" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="P34" s="2"/>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="2"/>
-      <c r="V34" s="1"/>
-    </row>
-    <row r="35" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="P35" s="2"/>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="2"/>
-      <c r="V35" s="1"/>
-    </row>
-    <row r="36" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="P36" s="2"/>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="2"/>
-      <c r="V36" s="1"/>
-    </row>
-    <row r="37" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="P37" s="2"/>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="2"/>
-      <c r="V37" s="1"/>
-    </row>
-    <row r="38" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="1"/>
-    </row>
-    <row r="39" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="1"/>
-    </row>
-    <row r="40" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="P40" s="2"/>
-      <c r="Q40" s="2"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="2"/>
-      <c r="V40" s="1"/>
-    </row>
-    <row r="41" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="1"/>
-    </row>
-    <row r="42" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="P42" s="2"/>
-      <c r="Q42" s="2"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="2"/>
-      <c r="V42" s="1"/>
-    </row>
-    <row r="43" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="2"/>
-      <c r="V43" s="1"/>
-    </row>
-    <row r="44" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="P44" s="2"/>
-      <c r="Q44" s="2"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="2"/>
-      <c r="V44" s="1"/>
-    </row>
-    <row r="45" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="P45" s="2"/>
-      <c r="Q45" s="2"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="2"/>
-      <c r="V45" s="1"/>
-    </row>
-    <row r="46" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="P46" s="2"/>
-      <c r="Q46" s="2"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="8"/>
-      <c r="U46" s="2"/>
-      <c r="V46" s="1"/>
-    </row>
-    <row r="47" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="P47" s="2"/>
-      <c r="Q47" s="2"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="8"/>
-      <c r="U47" s="2"/>
-      <c r="V47" s="1"/>
-    </row>
-    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="P48" s="2"/>
-      <c r="Q48" s="2"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="8"/>
-      <c r="U48" s="2"/>
-      <c r="V48" s="1"/>
-    </row>
-    <row r="49" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="P49" s="2"/>
-      <c r="Q49" s="2"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="8"/>
-      <c r="U49" s="2"/>
-      <c r="V49" s="1"/>
-    </row>
-    <row r="50" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="P50" s="2"/>
-      <c r="Q50" s="2"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="8"/>
-      <c r="U50" s="2"/>
-      <c r="V50" s="1"/>
-    </row>
-    <row r="51" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="9"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="8"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="1"/>
-    </row>
-    <row r="52" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="9"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="P52" s="2"/>
-      <c r="Q52" s="2"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="1"/>
-      <c r="T52" s="8"/>
-      <c r="U52" s="2"/>
-      <c r="V52" s="1"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{36A71429-8BE7-41F0-AAE4-D3A65285DA9E}"/>
-    <hyperlink ref="D7" r:id="rId2" location=":~:text=%D0%9E%D0%BF%D0%B5%D1%80%D0%B0%D1%82%D0%BE%D1%80%D1%8B%20BREAK%20%D0%B8%20CONTINUE" xr:uid="{E48C9FD6-2CCF-4B4D-B673-A7B60297A76A}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -72007,7 +71471,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="40" type="noConversion"/>
+  <phoneticPr fontId="42" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="D46" r:id="rId1" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85" xr:uid="{FDFE2116-2B22-4A87-B37D-3DFA9E8F9FE0}"/>
     <hyperlink ref="D44" r:id="rId2" location=":~:text=%D0%A1%D0%BE%D0%B7%D0%B4%D0%B0%D0%BD%D0%B8%D0%B5%20%D0%B1%D0%B0%D0%B7%D1%8B%20%D0%B4%D0%B0%D0%BD%D0%BD%D1%8B%D1%85%20%D0%B2%20SQL%20Management%20Studio" xr:uid="{5B701F02-CEF7-44EA-83C6-0E21D7145608}"/>
@@ -72021,6 +71485,876 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B39B1FF9-091B-40BE-9FD0-8662822E487B}">
+  <sheetPr>
+    <tabColor rgb="FF7030A0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:V52"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="8"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="70" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="P3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="2"/>
+    </row>
+    <row r="4" spans="1:22" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="108" t="s">
+        <v>1234</v>
+      </c>
+      <c r="P4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="2"/>
+    </row>
+    <row r="5" spans="1:22" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="108" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C5" s="108" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:22" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="108" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C6" s="108" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="107" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="69" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="108" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="1"/>
+    </row>
+    <row r="22" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="1"/>
+    </row>
+    <row r="24" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="1"/>
+    </row>
+    <row r="25" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="1"/>
+    </row>
+    <row r="27" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="1"/>
+    </row>
+    <row r="28" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="1"/>
+    </row>
+    <row r="29" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="1"/>
+    </row>
+    <row r="30" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="8"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="1"/>
+    </row>
+    <row r="33" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="8"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="1"/>
+    </row>
+    <row r="34" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="1"/>
+    </row>
+    <row r="36" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="1"/>
+    </row>
+    <row r="37" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="8"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="1"/>
+    </row>
+    <row r="38" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="1"/>
+    </row>
+    <row r="39" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="8"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="1"/>
+    </row>
+    <row r="40" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="1"/>
+    </row>
+    <row r="41" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="1"/>
+    </row>
+    <row r="42" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="1"/>
+    </row>
+    <row r="45" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="1"/>
+    </row>
+    <row r="46" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="1"/>
+    </row>
+    <row r="47" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="8"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="1"/>
+    </row>
+    <row r="48" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="1"/>
+    </row>
+    <row r="49" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="8"/>
+      <c r="U49" s="2"/>
+      <c r="V49" s="1"/>
+    </row>
+    <row r="50" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="8"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="1"/>
+    </row>
+    <row r="51" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="8"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="1"/>
+    </row>
+    <row r="52" spans="1:22" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{36A71429-8BE7-41F0-AAE4-D3A65285DA9E}"/>
+    <hyperlink ref="D7" r:id="rId2" location=":~:text=%D0%9E%D0%BF%D0%B5%D1%80%D0%B0%D1%82%D0%BE%D1%80%D1%8B%20BREAK%20%D0%B8%20CONTINUE" xr:uid="{E48C9FD6-2CCF-4B4D-B673-A7B60297A76A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{714A04EA-98A4-480D-A5F1-767156A145A3}">
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
@@ -72159,7 +72493,7 @@
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:22" ht="144" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="B11" s="108" t="s">
         <v>1253</v>
@@ -72900,7 +73234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1027220B-EA3D-44CD-AA33-1660B4C18903}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -73811,7 +74145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2031D5F9-8A97-4E56-9A45-BE47502C97DA}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
@@ -74761,7 +75095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01B65FF-3E11-4C6D-98D7-9E777AE32C33}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -75052,7 +75386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{406FA542-E35D-441D-A937-7835B6AE1BC8}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -75149,6 +75483,9 @@
       <c r="D6" s="108"/>
     </row>
     <row r="7" spans="1:21" ht="216" x14ac:dyDescent="0.3">
+      <c r="B7" s="200" t="s">
+        <v>1869</v>
+      </c>
       <c r="C7" s="122" t="s">
         <v>1310</v>
       </c>
@@ -75484,7 +75821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE588444-EB12-4F5B-BFC6-A3A54FCA276B}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -75939,7 +76276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB01197-FE1C-4ED1-B3B4-7B774B71A2A6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -75990,7 +76327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8347859-D7B0-40A5-9B17-0069AC1E92BB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -76355,7 +76692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AAE27B-B1A5-470A-8C56-1AC981AA4A71}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -76691,7 +77028,480 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE7095F-8B4B-470C-B9E5-197B8CFF3B58}">
+  <sheetPr>
+    <tabColor theme="5"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:E48"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36" style="2" customWidth="1"/>
+    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.21875" style="46" customWidth="1"/>
+    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
+    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.77734375" style="2"/>
+    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
+    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
+    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
+    <col min="28" max="16384" width="8.77734375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="46"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="47" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="47" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="47" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="47" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="34" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="B32" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="48" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C34" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="48" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C36" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="48" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C38" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="47" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D40" s="69" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="42" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D40" r:id="rId1" location=":~:text=%D0%94%D0%BB%D1%8F%20%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D1%86%D0%B8%D0%B8%20%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82%D0%B0%20UNIQUEIDENTIFIER" xr:uid="{8276130C-D262-49CA-89B1-D60C8C3E4E63}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B13A24C-6305-48F4-A1E6-55B31CAA1F4A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -77564,480 +78374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EE7095F-8B4B-470C-B9E5-197B8CFF3B58}">
-  <sheetPr>
-    <tabColor theme="5"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E48"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="46" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="46"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="47" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="47" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="47" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="47" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="34" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="B32" s="42" t="s">
-        <v>321</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="48" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C34" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="48" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C36" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="48" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C38" s="2" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="47" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D40" s="69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="40" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D40" r:id="rId1" location=":~:text=%D0%94%D0%BB%D1%8F%20%D0%B3%D0%B5%D0%BD%D0%B5%D1%80%D0%B0%D1%86%D0%B8%D0%B8%20%D0%BE%D0%B1%D1%8A%D0%B5%D0%BA%D1%82%D0%B0%20UNIQUEIDENTIFIER" xr:uid="{8276130C-D262-49CA-89B1-D60C8C3E4E63}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA83B601-5B0E-4344-A36B-7DD0432A3007}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -81527,154 +81864,19 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EA6674-336F-4905-8CC7-BE3D2DB29BA7}">
-  <sheetPr>
-    <tabColor theme="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:E13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3670A74-83EB-4724-95EA-CCDAFBAF79BA}">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36" style="2" customWidth="1"/>
-    <col min="2" max="2" width="50.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="71.21875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="56.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.21875" style="46" customWidth="1"/>
-    <col min="6" max="6" width="43.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="67.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="64.33203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="39.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="48.88671875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="72.6640625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="43.88671875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.77734375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="46.77734375" style="2" customWidth="1"/>
-    <col min="18" max="18" width="62.88671875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="49.21875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.77734375" style="2"/>
-    <col min="21" max="21" width="67.77734375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="68.33203125" style="2" customWidth="1"/>
-    <col min="23" max="24" width="59.33203125" style="2" customWidth="1"/>
-    <col min="25" max="25" width="59.6640625" style="2" customWidth="1"/>
-    <col min="26" max="26" width="99.44140625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="41.21875" style="2" customWidth="1"/>
-    <col min="28" max="16384" width="8.77734375" style="2"/>
+    <col min="2" max="2" width="76.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" s="45" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E2" s="46"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
-        <v>488</v>
-      </c>
-      <c r="D3" s="69" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C4" s="66" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46" t="s">
-        <v>490</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>493</v>
-      </c>
-      <c r="D5" s="46"/>
-    </row>
-    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="B6" s="66" t="s">
-        <v>499</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="D6" s="66" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="B7" s="66" t="s">
-        <v>498</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="D7" s="66" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D8" s="66" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="C9" s="146" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="C10" s="79" t="s">
-        <v>719</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="B11" s="66" t="s">
-        <v>505</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C13" s="2" t="s">
-        <v>513</v>
+    <row r="2" spans="2:2" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="201" t="s">
+        <v>1870</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" xr:uid="{71703303-5B70-4508-9FB9-E0DF58B4FD29}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>